--- a/human_validation/judge/en/judge_D008_S002_P001__llama-3.3-70b-instruct.xlsx
+++ b/human_validation/judge/en/judge_D008_S002_P001__llama-3.3-70b-instruct.xlsx
@@ -461,6 +461,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -556,6 +557,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
